--- a/database/datas-primaire.xlsx
+++ b/database/datas-primaire.xlsx
@@ -2,6 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
+  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="xANYWrTOsg63XXkjDRwicyQiy99h3p7M5l5KYDoNXnbZVJozsb69/5yT31adgC5KeR6Iu3ESchNPP/iCFsCaBA==" workbookSaltValue="W/S3V8XYl5DPmF/07lR17A==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
@@ -35455,13 +35456,13 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2" disablePrompts="0">
-        <x14:dataValidation xr:uid="{CC619231-4549-47A3-8176-64CACAEBE71D}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{838A9397-771F-4FDA-9067-F6737FC8D876}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>"1ère,2ème,3ème,4ème,5ème,6ème"</xm:f>
           </x14:formula1>
           <xm:sqref>N8:N1021 N1022 N1023 N1024 N1025 N1026 N1027 N1028 N1029 N1030 N1031 N1032 N1033 N1034 N1035 N1036 N1037 N1038 N1039 N1040 N1041 N1042 N1043 N1044 N1045 N1046 N1047 N1048 N1049 N1050 N1051 N1052 N1053 N1054 N1055 N1056 N1057 N1058 N1059 N1060 N1061 N1062 N1063 N1064 N1065 N1066 N1067 N1068 N1069 N1070 N1071 N1072 N1073 N1074 N1075 N1076 N1077 N1078 N1079 N1080 N1081 N1082 N1083 N1084 N1085 N1086 N1087 N1088 N1089 N1090 N1091 N1092 N1093 N1094 N1095 N1096 N1097 N1098 N1099 N1100 N1101 N1102 N1103 N1104 N1105 N1106 N1107 N1108 N1109 N1110 N1111 N1112 N1113 N1114 N1115 N1116 N1117 N1118 N1119 N1120 N1121 N1122 N1123 N1124 N1125 N1126 N1127 N1128 N1129 N1130 N1131 N1132 N1133 N1134 N1135 N1136 N1137 N1138 N1139 N1140 N1141 N1142 N1143 N1144 N1145 N1146 N1147 N1148 N1149 N1150 N1151 N1152 N1153 N1154 N1155 N1156 N1157 N1158 N1159 N1160 N1161 N1162 N1163 N1164 N1165 N1166 N1167 N1168 N1169 N1170 N1171 N1172 N1173 N1174 N1175 N1176 N1177 N1178 N1179 N1180 N1181 N1182 N1183 N1184 N1185 N1186 N1187 N1188 N1189 N1190 N1191 N1192 N1193 N1194 N1195 N1196 N1197 N1198 N1199 N1200 N1201 N1202 N1203 N1204 N1205 N1206 N1207 N1208 N1209 N1210 N1211 N1212 N1213 N1214 N1215 N1216 N1217 N1218 N1219 N1220 N1221 N1222 N1223 N1224 N1225 N1226 N1227 N1228 N1229 N1230 N1231 N1232 N1233 N1234 N1235 N1236 N1237 N1238 N1239 N1240 N1241 N1242 N1243 N1244 N1245 N1246 N1247 N1248 N1249 N1250 N1251 N1252 N1253 N1254 N1255 N1256 N1257 N1258 N1259 N1260 N1261 N1262 N1263 N1264 N1265 N1266 N1267 N1268 N1269 N1270 N1271 N1272 N1273 N1274 N1275 N1276 N1277 N1278 N1279 N1280 N1281 N1282 N1283 N1284 N1285 N1286 N1287 N1288 N1289 N1290 N1291 N1292 N1293 N1294 N1295 N1296 N1297 N1298 N1299 N1300 N1301 N1302 N1303 N1304 N1305 N1306 N1307 N1308 N1309 N1310 N1311 N1312 N1313 N1314 N1315 N1316 N1317 N1318 N1319 N1320 N1321 N1322 N1323 N1324 N1325 N1326 N1327 N1328 N1329 N1330 N1331 N1332 N1333 N1334 N1335 N1336 N1337 N1338 N1339 N1340 N1341 N1342 N1343 N1344 N1345 N1346 N1347 N1348 N1349 N1350 N1351 N1352 N1353 N1354 N1355 N1356 N1357 N1358 N1359 N1360 N1361 N1362 N1363 N1364 N1365 N1366 N1367 N1368 N1369 N1370 N1371 N1372 N1373 N1374 N1375 N1376 N1377 N1378 N1379 N1380 N1381 N1382 N1383 N1384 N1385 N1386 N1387 N1388 N1389 N1390 N1391 N1392 N1393 N1394 N1395 N1396 N1397 N1398 N1399 N1400 N1401 N1402 N1403 N1404 N1405 N1406 N1407 N1408 N1409 N1410 N1411 N1412 N1413 N1414 N1415 N1416 N1417 N1418 N1419 N1420 N1421 N1422 N1423 N1424 N1425 N1426 N1427 N1428 N1429 N1430 N1431 N1432 N1433 N1434 N1435 N1436 N1437 N1438 N1439 N1440 N1441 N1442 N1443 N1444 N1445 N1446 N1447 N1448 N1449 N1450 N1451 N1452 N1453 N1454 N1455 N1456 N1457 N1458 N1459 N1460 N1461 N1462 N1463 N1464 N1465 N1466 N1467 N1468 N1469 N1470 N1471 N1472 N1473 N1474 N1475 N1476 N1477 N1478 N1479 N1480 N1481 N1482 N1483 N1484 N1485 N1486 N1487 N1488 N1489 N1490 N1491 N1492 N1493 N1494 N1495 N1496 N1497 N1498 N1499 N1500</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{16F75EFE-626E-43C6-89B7-1149298C4F0D}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{5B6802C8-6763-4C90-B863-3AE156CC060B}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>"M,F"</xm:f>
           </x14:formula1>

--- a/database/datas-primaire.xlsx
+++ b/database/datas-primaire.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t xml:space="preserve">LISTE D'ELEVES | PRIMAIRE</t>
   </si>
@@ -41,6 +41,30 @@
   </si>
   <si>
     <t>OPTION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MUKUMA MUKAZO</t>
+  </si>
+  <si>
+    <t>AARON</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>17,Ngalula/Kabulameshi/Lubumbashi/RDC</t>
+  </si>
+  <si>
+    <t>6ème</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSHINDJI SATSHINYEKE</t>
+  </si>
+  <si>
+    <t>MARDOCHEE</t>
+  </si>
+  <si>
+    <t>1ère</t>
   </si>
 </sst>
 </file>
@@ -982,19 +1006,31 @@
       <c r="S7" s="3"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="B8" s="11"/>
+      <c r="B8" s="11" t="s">
+        <v>8</v>
+      </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
       <c r="F8" s="12"/>
-      <c r="G8" s="11"/>
+      <c r="G8" s="11" t="s">
+        <v>9</v>
+      </c>
       <c r="H8" s="12"/>
-      <c r="I8" s="13"/>
+      <c r="I8" s="13">
+        <v>42687</v>
+      </c>
       <c r="J8" s="14"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="11"/>
+      <c r="K8" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>11</v>
+      </c>
       <c r="M8" s="12"/>
-      <c r="N8" s="14"/>
+      <c r="N8" s="14" t="s">
+        <v>12</v>
+      </c>
       <c r="O8" s="16"/>
       <c r="P8" s="16"/>
       <c r="Q8" s="16"/>
@@ -1002,19 +1038,31 @@
       <c r="S8" s="16"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="B9" s="17"/>
+      <c r="B9" s="17" t="s">
+        <v>13</v>
+      </c>
       <c r="C9" s="17"/>
       <c r="D9" s="17"/>
       <c r="E9" s="17"/>
       <c r="F9" s="18"/>
-      <c r="G9" s="17"/>
+      <c r="G9" s="17" t="s">
+        <v>14</v>
+      </c>
       <c r="H9" s="18"/>
-      <c r="I9" s="19"/>
+      <c r="I9" s="19">
+        <v>44532</v>
+      </c>
       <c r="J9" s="20"/>
-      <c r="K9" s="21"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="18"/>
-      <c r="N9" s="22"/>
+      <c r="K9" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="M9" s="12"/>
+      <c r="N9" s="22" t="s">
+        <v>15</v>
+      </c>
       <c r="O9" s="16"/>
       <c r="P9" s="16"/>
       <c r="Q9" s="16"/>
@@ -35456,13 +35504,13 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2" disablePrompts="0">
-        <x14:dataValidation xr:uid="{838A9397-771F-4FDA-9067-F6737FC8D876}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{90B01068-472F-4B48-B69D-AF1849C7633C}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>"1ère,2ème,3ème,4ème,5ème,6ème"</xm:f>
           </x14:formula1>
           <xm:sqref>N8:N1021 N1022 N1023 N1024 N1025 N1026 N1027 N1028 N1029 N1030 N1031 N1032 N1033 N1034 N1035 N1036 N1037 N1038 N1039 N1040 N1041 N1042 N1043 N1044 N1045 N1046 N1047 N1048 N1049 N1050 N1051 N1052 N1053 N1054 N1055 N1056 N1057 N1058 N1059 N1060 N1061 N1062 N1063 N1064 N1065 N1066 N1067 N1068 N1069 N1070 N1071 N1072 N1073 N1074 N1075 N1076 N1077 N1078 N1079 N1080 N1081 N1082 N1083 N1084 N1085 N1086 N1087 N1088 N1089 N1090 N1091 N1092 N1093 N1094 N1095 N1096 N1097 N1098 N1099 N1100 N1101 N1102 N1103 N1104 N1105 N1106 N1107 N1108 N1109 N1110 N1111 N1112 N1113 N1114 N1115 N1116 N1117 N1118 N1119 N1120 N1121 N1122 N1123 N1124 N1125 N1126 N1127 N1128 N1129 N1130 N1131 N1132 N1133 N1134 N1135 N1136 N1137 N1138 N1139 N1140 N1141 N1142 N1143 N1144 N1145 N1146 N1147 N1148 N1149 N1150 N1151 N1152 N1153 N1154 N1155 N1156 N1157 N1158 N1159 N1160 N1161 N1162 N1163 N1164 N1165 N1166 N1167 N1168 N1169 N1170 N1171 N1172 N1173 N1174 N1175 N1176 N1177 N1178 N1179 N1180 N1181 N1182 N1183 N1184 N1185 N1186 N1187 N1188 N1189 N1190 N1191 N1192 N1193 N1194 N1195 N1196 N1197 N1198 N1199 N1200 N1201 N1202 N1203 N1204 N1205 N1206 N1207 N1208 N1209 N1210 N1211 N1212 N1213 N1214 N1215 N1216 N1217 N1218 N1219 N1220 N1221 N1222 N1223 N1224 N1225 N1226 N1227 N1228 N1229 N1230 N1231 N1232 N1233 N1234 N1235 N1236 N1237 N1238 N1239 N1240 N1241 N1242 N1243 N1244 N1245 N1246 N1247 N1248 N1249 N1250 N1251 N1252 N1253 N1254 N1255 N1256 N1257 N1258 N1259 N1260 N1261 N1262 N1263 N1264 N1265 N1266 N1267 N1268 N1269 N1270 N1271 N1272 N1273 N1274 N1275 N1276 N1277 N1278 N1279 N1280 N1281 N1282 N1283 N1284 N1285 N1286 N1287 N1288 N1289 N1290 N1291 N1292 N1293 N1294 N1295 N1296 N1297 N1298 N1299 N1300 N1301 N1302 N1303 N1304 N1305 N1306 N1307 N1308 N1309 N1310 N1311 N1312 N1313 N1314 N1315 N1316 N1317 N1318 N1319 N1320 N1321 N1322 N1323 N1324 N1325 N1326 N1327 N1328 N1329 N1330 N1331 N1332 N1333 N1334 N1335 N1336 N1337 N1338 N1339 N1340 N1341 N1342 N1343 N1344 N1345 N1346 N1347 N1348 N1349 N1350 N1351 N1352 N1353 N1354 N1355 N1356 N1357 N1358 N1359 N1360 N1361 N1362 N1363 N1364 N1365 N1366 N1367 N1368 N1369 N1370 N1371 N1372 N1373 N1374 N1375 N1376 N1377 N1378 N1379 N1380 N1381 N1382 N1383 N1384 N1385 N1386 N1387 N1388 N1389 N1390 N1391 N1392 N1393 N1394 N1395 N1396 N1397 N1398 N1399 N1400 N1401 N1402 N1403 N1404 N1405 N1406 N1407 N1408 N1409 N1410 N1411 N1412 N1413 N1414 N1415 N1416 N1417 N1418 N1419 N1420 N1421 N1422 N1423 N1424 N1425 N1426 N1427 N1428 N1429 N1430 N1431 N1432 N1433 N1434 N1435 N1436 N1437 N1438 N1439 N1440 N1441 N1442 N1443 N1444 N1445 N1446 N1447 N1448 N1449 N1450 N1451 N1452 N1453 N1454 N1455 N1456 N1457 N1458 N1459 N1460 N1461 N1462 N1463 N1464 N1465 N1466 N1467 N1468 N1469 N1470 N1471 N1472 N1473 N1474 N1475 N1476 N1477 N1478 N1479 N1480 N1481 N1482 N1483 N1484 N1485 N1486 N1487 N1488 N1489 N1490 N1491 N1492 N1493 N1494 N1495 N1496 N1497 N1498 N1499 N1500</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{5B6802C8-6763-4C90-B863-3AE156CC060B}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{A0CBF364-DBA3-477A-8679-49FC5C90352A}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>"M,F"</xm:f>
           </x14:formula1>
